--- a/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E2F38B0-4986-4EBA-ACA2-2B8E1031853A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9345"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KNSA" sheetId="6" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
   <si>
     <t>KNSA</t>
   </si>
@@ -303,7 +304,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -369,9 +370,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -409,9 +410,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -446,7 +447,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -481,7 +482,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -654,9 +655,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -689,21 +690,20 @@
     <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="42" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
@@ -815,17 +815,8 @@
       <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP7" s="2" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -937,17 +928,8 @@
       <c r="AM8" s="3">
         <v>0</v>
       </c>
-      <c r="AN8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP8" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -1059,17 +1041,8 @@
       <c r="AM9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP9" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,17 +1154,8 @@
       <c r="AM10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP10" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1231,11 +1195,8 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
-      <c r="AN11" s="3"/>
-      <c r="AO11" s="3"/>
-      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1347,17 +1308,8 @@
       <c r="AM12" s="3">
         <v>9300</v>
       </c>
-      <c r="AN12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP12" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1469,17 +1421,8 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
-      <c r="AN13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO13" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP13" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1591,17 +1534,8 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1713,17 +1647,8 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
-      <c r="AN15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1760,11 +1685,8 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
-      <c r="AN16" s="3"/>
-      <c r="AO16" s="3"/>
-      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1876,17 +1798,8 @@
       <c r="AM17" s="3">
         <v>11400</v>
       </c>
-      <c r="AN17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP17" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1998,17 +1911,8 @@
       <c r="AM18" s="3">
         <v>-11400</v>
       </c>
-      <c r="AN18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP18" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2048,11 +1952,8 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
-      <c r="AN19" s="3"/>
-      <c r="AO19" s="3"/>
-      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2164,17 +2065,8 @@
       <c r="AM20" s="3">
         <v>200</v>
       </c>
-      <c r="AN20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP20" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2286,17 +2178,8 @@
       <c r="AM21" s="3">
         <v>-11200</v>
       </c>
-      <c r="AN21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP21" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2408,17 +2291,8 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
-      <c r="AN22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP22" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2530,17 +2404,8 @@
       <c r="AM23" s="3">
         <v>-11200</v>
       </c>
-      <c r="AN23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP23" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2652,17 +2517,8 @@
       <c r="AM24" s="3">
         <v>0</v>
       </c>
-      <c r="AN24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP24" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2774,17 +2630,8 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
-      <c r="AN25" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO25" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP25" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2896,17 +2743,8 @@
       <c r="AM26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AN26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP26" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -3018,17 +2856,8 @@
       <c r="AM27" s="3">
         <v>-11200</v>
       </c>
-      <c r="AN27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP27" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3140,17 +2969,8 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
-      <c r="AN28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP28" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3262,17 +3082,8 @@
       <c r="AM29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP29" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3384,17 +3195,8 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
-      <c r="AN30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP30" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3506,17 +3308,8 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
-      <c r="AN31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO31" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP31" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3628,17 +3421,8 @@
       <c r="AM32" s="3">
         <v>-200</v>
       </c>
-      <c r="AN32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP32" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3750,17 +3534,8 @@
       <c r="AM33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AN33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP33" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3872,17 +3647,8 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
-      <c r="AN34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP34" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3994,22 +3760,13 @@
       <c r="AM35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AN35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP35" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
@@ -4121,17 +3878,8 @@
       <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP38" s="2" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4171,11 +3919,8 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
-      <c r="AN39" s="3"/>
-      <c r="AO39" s="3"/>
-      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4215,11 +3960,8 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
-      <c r="AN40" s="3"/>
-      <c r="AO40" s="3"/>
-      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -4331,17 +4073,8 @@
       <c r="AM41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP41" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4453,17 +4186,8 @@
       <c r="AM42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP42" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4575,17 +4299,8 @@
       <c r="AM43" s="3">
         <v>0</v>
       </c>
-      <c r="AN43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO43" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP43" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4697,17 +4412,8 @@
       <c r="AM44" s="3">
         <v>0</v>
       </c>
-      <c r="AN44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO44" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP44" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4819,17 +4525,8 @@
       <c r="AM45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP45" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4941,17 +4638,8 @@
       <c r="AM46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP46" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -5063,17 +4751,8 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
-      <c r="AN47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP47" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -5185,17 +4864,8 @@
       <c r="AM48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP48" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -5307,17 +4977,8 @@
       <c r="AM49" s="3">
         <v>0</v>
       </c>
-      <c r="AN49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP49" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5429,17 +5090,8 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
-      <c r="AN50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO50" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP50" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5551,17 +5203,8 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
-      <c r="AN51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO51" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP51" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5673,17 +5316,8 @@
       <c r="AM52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP52" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5795,17 +5429,8 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
-      <c r="AN53" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO53" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP53" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -5917,17 +5542,8 @@
       <c r="AM54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP54" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5967,11 +5583,8 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
-      <c r="AN55" s="3"/>
-      <c r="AO55" s="3"/>
-      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6011,11 +5624,8 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
-      <c r="AN56" s="3"/>
-      <c r="AO56" s="3"/>
-      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -6127,17 +5737,8 @@
       <c r="AM57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP57" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6249,17 +5850,8 @@
       <c r="AM58" s="3">
         <v>0</v>
       </c>
-      <c r="AN58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP58" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -6371,17 +5963,8 @@
       <c r="AM59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP59" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -6493,17 +6076,8 @@
       <c r="AM60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP60" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -6615,17 +6189,8 @@
       <c r="AM61" s="3">
         <v>0</v>
       </c>
-      <c r="AN61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP61" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6737,17 +6302,8 @@
       <c r="AM62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP62" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6859,17 +6415,8 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
-      <c r="AN63" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO63" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP63" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6981,17 +6528,8 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
-      <c r="AN64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO64" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP64" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7103,17 +6641,8 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
-      <c r="AN65" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO65" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP65" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -7225,17 +6754,8 @@
       <c r="AM66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP66" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7275,11 +6795,8 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
-      <c r="AN67" s="3"/>
-      <c r="AO67" s="3"/>
-      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7391,17 +6908,8 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
-      <c r="AN68" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO68" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP68" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7513,17 +7021,8 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
-      <c r="AN69" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO69" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP69" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7635,17 +7134,8 @@
       <c r="AM70" s="3">
         <v>0</v>
       </c>
-      <c r="AN70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO70" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP70" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7757,17 +7247,8 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
-      <c r="AN71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO71" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP71" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7879,17 +7360,8 @@
       <c r="AM72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP72" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8001,17 +7473,8 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
-      <c r="AN73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO73" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP73" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8123,17 +7586,8 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
-      <c r="AN74" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO74" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP74" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8245,17 +7699,8 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
-      <c r="AN75" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO75" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP75" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -8367,17 +7812,8 @@
       <c r="AM76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AN76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP76" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8489,22 +7925,13 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
-      <c r="AN77" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO77" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP77" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
@@ -8616,17 +8043,8 @@
       <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP80" s="2" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8738,17 +8156,8 @@
       <c r="AM81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AN81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP81" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8788,11 +8197,8 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
-      <c r="AN82" s="3"/>
-      <c r="AO82" s="3"/>
-      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -8904,17 +8310,8 @@
       <c r="AM83" s="3">
         <v>0</v>
       </c>
-      <c r="AN83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP83" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9026,17 +8423,8 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
-      <c r="AN84" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO84" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP84" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9148,17 +8536,8 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
-      <c r="AN85" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO85" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP85" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9270,17 +8649,8 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
-      <c r="AN86" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO86" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP86" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9392,17 +8762,8 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
-      <c r="AN87" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO87" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP87" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9514,17 +8875,8 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
-      <c r="AN88" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO88" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP88" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -9636,17 +8988,8 @@
       <c r="AM89" s="3">
         <v>-10200</v>
       </c>
-      <c r="AN89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP89" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9686,11 +9029,8 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
-      <c r="AN90" s="3"/>
-      <c r="AO90" s="3"/>
-      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9802,17 +9142,8 @@
       <c r="AM91" s="3">
         <v>0</v>
       </c>
-      <c r="AN91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP91" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9924,17 +9255,8 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
-      <c r="AN92" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO92" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP92" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10046,17 +9368,8 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
-      <c r="AN93" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO93" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP93" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -10168,17 +9481,8 @@
       <c r="AM94" s="3">
         <v>0</v>
       </c>
-      <c r="AN94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP94" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10218,11 +9522,8 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
-      <c r="AN95" s="3"/>
-      <c r="AO95" s="3"/>
-      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10334,17 +9635,8 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
-      <c r="AN96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP96" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10456,17 +9748,8 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
-      <c r="AN97" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO97" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP97" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10578,17 +9861,8 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
-      <c r="AN98" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO98" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP98" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10700,17 +9974,8 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
-      <c r="AN99" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO99" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP99" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -10822,17 +10087,8 @@
       <c r="AM100" s="3">
         <v>0</v>
       </c>
-      <c r="AN100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP100" s="3" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10944,17 +10200,8 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
-      <c r="AN101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP101" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -11065,15 +10312,6 @@
       </c>
       <c r="AM102" s="3">
         <v>-10200</v>
-      </c>
-      <c r="AN102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AO102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AP102" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNSA_QTR_FIN.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E2F38B0-4986-4EBA-ACA2-2B8E1031853A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="KNSA" sheetId="6" r:id="rId1"/>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
   <si>
     <t>KNSA</t>
   </si>
@@ -304,7 +303,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
@@ -370,9 +369,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -410,9 +409,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -447,7 +446,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -482,7 +481,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -655,234 +654,238 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AM102"/>
+  <dimension ref="A5:AN102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>243600</v>
+      </c>
+      <c r="E8" s="3">
         <v>214300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>202100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>180900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>156800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>137800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>122500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>112200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>108600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>79900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>83400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>67000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>71500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>48300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>61900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>99100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>27000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>32200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>18700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>12100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7700</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -898,8 +901,8 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD8" s="3">
-        <v>0</v>
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE8" s="3">
         <v>0</v>
@@ -928,74 +931,77 @@
       <c r="AM8" s="3">
         <v>0</v>
       </c>
+      <c r="AN8" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>111600</v>
+      </c>
+      <c r="E9" s="3">
         <v>96400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>91000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>83600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>71000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>61700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>66100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>49400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>42300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>31400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>26500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>21700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>6900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2500</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -1041,74 +1047,77 @@
       <c r="AM9" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN9" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>132000</v>
+      </c>
+      <c r="E10" s="3">
         <v>117900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>111200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>97300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>85800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>76100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>56500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>62800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>66300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>48500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>56900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>40600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>49800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>33000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>55200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>92200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>22000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>28000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>14800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>9300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>5200</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1154,8 +1163,11 @@
       <c r="AM10" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN10" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1195,121 +1207,125 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E12" s="3">
         <v>27500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>34600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>24200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>18800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>19300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>35200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>26100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>24000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>26300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>20100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>17100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>23800</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>15200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>14400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>16500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>13800</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>20800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>27400</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>19200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>23900</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>28700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>37400</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>31400</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>22300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>20900</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>22900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>22000</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>30800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>59300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>36100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>20600</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>12600</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>56400</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>14000</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>9300</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1421,8 +1437,11 @@
       <c r="AM13" s="3">
         <v>0</v>
       </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1465,8 +1484,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1504,8 +1523,8 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>3</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>3</v>
@@ -1516,8 +1535,8 @@
       <c r="AG14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1534,8 +1553,11 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1546,16 +1568,16 @@
         <v>500</v>
       </c>
       <c r="F15" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G15" s="3">
         <v>400</v>
       </c>
       <c r="H15" s="3">
+        <v>400</v>
+      </c>
+      <c r="I15" s="3">
         <v>300</v>
-      </c>
-      <c r="I15" s="3">
-        <v>400</v>
       </c>
       <c r="J15" s="3">
         <v>400</v>
@@ -1564,13 +1586,13 @@
         <v>400</v>
       </c>
       <c r="L15" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="M15" s="3">
         <v>500</v>
       </c>
       <c r="N15" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="O15" s="3">
         <v>600</v>
@@ -1579,7 +1601,7 @@
         <v>600</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1647,8 +1669,11 @@
       <c r="AM15" s="3">
         <v>0</v>
       </c>
+      <c r="AN15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1685,187 +1710,191 @@
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
     </row>
-    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>216400</v>
+      </c>
+      <c r="E17" s="3">
         <v>185000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>182400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>156800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>136600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>124500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>141800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>121900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>108700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>96400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>83300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>78000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>74600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>59500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>55800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>52700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>46300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>55500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>54900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>42800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>48300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>49300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>52900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>43200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>31900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>29400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>32600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>30400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>39300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>67600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>44100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>26200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>21500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>16300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>65400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>16200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E18" s="3">
         <v>29300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>19800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>24000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>20200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-19300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-9700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-16500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>6100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>46400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-19300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-23300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-36200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-30700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-40600</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1881,38 +1910,41 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE18" s="3">
         <v>-30400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-39300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-67600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-44100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-26200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-21500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-16300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-65400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-16200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>-11400</v>
       </c>
     </row>
-    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1952,73 +1984,74 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
     </row>
-    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2700</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-2300</v>
       </c>
       <c r="I20" s="3">
         <v>-2300</v>
       </c>
       <c r="J20" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="K20" s="3">
         <v>-2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2300</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-2400</v>
       </c>
       <c r="N20" s="3">
         <v>-2400</v>
       </c>
       <c r="O20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
         <v>0</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
@@ -2035,104 +2068,107 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE20" s="3">
         <v>1400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>1700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>500</v>
-      </c>
-      <c r="AL20" s="3">
-        <v>200</v>
       </c>
       <c r="AM20" s="3">
         <v>200</v>
       </c>
+      <c r="AN20" s="3">
+        <v>200</v>
+      </c>
     </row>
-    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E21" s="3">
         <v>33100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>23700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>27500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>23200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>15900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-16600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-6800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-13800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>47200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-18600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-22600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-35400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-30000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-39800</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -2148,38 +2184,41 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE21" s="3">
         <v>-28500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-37100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-65400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-42200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-24500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-20400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>-64800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>-16100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2222,8 +2261,8 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2291,222 +2330,228 @@
       <c r="AM22" s="3">
         <v>0</v>
       </c>
+      <c r="AN22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>31100</v>
+      </c>
+      <c r="E23" s="3">
         <v>32700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>23300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>27200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>22900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>15600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-17000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>6800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>46700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-19300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-23300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-36100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-30700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-40500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-49300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-52900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-43200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-31600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-28600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-31500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-29100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-37600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-65800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-42400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-24500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-20500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-64900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-16100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E24" s="3">
         <v>10100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-8100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-22800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-16200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-177400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-2000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-400</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-200</v>
-      </c>
-      <c r="AJ24" s="3">
-        <v>-100</v>
       </c>
       <c r="AK24" s="3">
         <v>-100</v>
@@ -2515,10 +2560,13 @@
         <v>-100</v>
       </c>
       <c r="AM24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AN24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2630,234 +2678,243 @@
       <c r="AM25" s="3">
         <v>0</v>
       </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E26" s="3">
         <v>22600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>14200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>18400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>8500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-8900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-12700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-17700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>25200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>15000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>224100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-20000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-25200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-36300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-30500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-41600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-49500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-53700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-43800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-37500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-26400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-31800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-27100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-37200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-65800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-42600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-24400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-20300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-64800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>-16000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E27" s="3">
         <v>22600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>14200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>18400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>8500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-8900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-12700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-17700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>25200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>15000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>224100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-20000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-25200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-36300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-30500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-41600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-49500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-53700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-43800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-37500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-26400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-31800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-27100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-37200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-65800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-24400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-20300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-64800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>-16000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2969,8 +3026,11 @@
       <c r="AM28" s="3">
         <v>0</v>
       </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3055,8 +3115,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>3</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>3</v>
@@ -3073,17 +3133,20 @@
       <c r="AJ29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-100</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN29" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3195,8 +3258,11 @@
       <c r="AM30" s="3">
         <v>0</v>
       </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3308,73 +3374,76 @@
       <c r="AM31" s="3">
         <v>0</v>
       </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E32" s="3">
         <v>3400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2700</v>
-      </c>
-      <c r="H32" s="3">
-        <v>2300</v>
       </c>
       <c r="I32" s="3">
         <v>2300</v>
       </c>
       <c r="J32" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K32" s="3">
         <v>2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2300</v>
-      </c>
-      <c r="M32" s="3">
-        <v>2400</v>
       </c>
       <c r="N32" s="3">
         <v>2400</v>
       </c>
       <c r="O32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="P32" s="3">
         <v>1900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
@@ -3391,151 +3460,157 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-500</v>
-      </c>
-      <c r="AL32" s="3">
-        <v>-200</v>
       </c>
       <c r="AM32" s="3">
         <v>-200</v>
       </c>
+      <c r="AN32" s="3">
+        <v>-200</v>
+      </c>
     </row>
-    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E33" s="3">
         <v>22600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>14200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>18400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>8500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-8900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-12700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-17700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>25200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>15000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>224100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-20000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-25200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-36300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-30500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-41600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-49500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-53700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-43800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-37500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-26400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-31800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-27100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-37200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-65800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-42600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-24400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-20300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-64900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-16000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3647,239 +3722,248 @@
       <c r="AM34" s="3">
         <v>0</v>
       </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E35" s="3">
         <v>22600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>14200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>18400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>8500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-8900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-12700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-17700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>25200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>15000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>224100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-20000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-25200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-36300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-30500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-41600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-49500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-53700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-43800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-37500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-26400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-31800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-27100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-37200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-65800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-42600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-24400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-20300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-64900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-16000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
     </row>
-    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3919,8 +4003,9 @@
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
     </row>
-    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3960,223 +4045,227 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
     </row>
-    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>175700</v>
+      </c>
+      <c r="E41" s="3">
         <v>190000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>165600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>174900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>192000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>157100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>183600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>97400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>99300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>141100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>108000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>117800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>112600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>80600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>122700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>175800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>94300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>63300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>122500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>190200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>168000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>119900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>114000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>85900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>123500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>106300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>46900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>68800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>82800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>82600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>72000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>69700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>285500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>221100</v>
       </c>
-      <c r="AK41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL41" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM41" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN41" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>350300</v>
+      </c>
+      <c r="E42" s="3">
         <v>278100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>248500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>177200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>115700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>111200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>60000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>126400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>119500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>72500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>98400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>83300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>72400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>106900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>67900</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>25000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>43900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>82300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>59700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>10000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>57900</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>144200</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>209400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>278500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>128900</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>97900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>186500</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>189900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>204600</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>243900</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>235300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>268200</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>73700</v>
       </c>
-      <c r="AJ42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AK42" s="3" t="s">
         <v>3</v>
       </c>
@@ -4186,74 +4275,77 @@
       <c r="AM42" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN42" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E43" s="3">
         <v>23200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>15600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>51700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>31900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>40100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>41700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>24900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>21300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>20300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>11200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>29400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>4000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>3200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2600</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -4269,8 +4361,8 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD43" s="3">
-        <v>0</v>
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE43" s="3">
         <v>0</v>
@@ -4299,77 +4391,80 @@
       <c r="AM43" s="3">
         <v>0</v>
       </c>
+      <c r="AN43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>70900</v>
+      </c>
+      <c r="E44" s="3">
         <v>73100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>54900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>41400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>48200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>22100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>26400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>28700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>34900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>27300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>31100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>25600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>24000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>23400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>21600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>14600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>19900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>13200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>6400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2200</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
@@ -4385,8 +4480,8 @@
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE44" s="3">
-        <v>0</v>
+      <c r="AE44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF44" s="3">
         <v>0</v>
@@ -4412,8 +4507,11 @@
       <c r="AM44" s="3">
         <v>0</v>
       </c>
+      <c r="AN44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4456,190 +4554,196 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
         <v>10500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>15300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>10500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>10000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>9400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>9800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>14000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>12100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>8800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>8200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>9600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>9000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>8400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>6400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1300</v>
       </c>
-      <c r="AK45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL45" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM45" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN45" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>668600</v>
+      </c>
+      <c r="E46" s="3">
         <v>594200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>527200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>475500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>420300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>355900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>331800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>311300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>301000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>270600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>276300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>256100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>246000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>231500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>243100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>241800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>179900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>198800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>196400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>217500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>244800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>275600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>333200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>378400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>264500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>213100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>241600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>268300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>296500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>335000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>313800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>341500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>363900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>222500</v>
       </c>
-      <c r="AK46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL46" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM46" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN46" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4682,8 +4786,8 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -4751,190 +4855,196 @@
       <c r="AM47" s="3">
         <v>0</v>
       </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E48" s="3">
         <v>11300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>11800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>11700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>11400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>11100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>11000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>11700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>12700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>7000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>9300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>9800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>10600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>8300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>8600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>8900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>100</v>
       </c>
-      <c r="AK48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL48" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM48" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN48" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>14800</v>
+      </c>
+      <c r="E49" s="3">
         <v>15000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>16000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>16300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>16500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>17000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>17300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>17500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>17800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>18000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>18300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>18500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>18800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>19000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>19300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>19500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>19800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>20000</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4950,8 +5060,8 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE49" s="3">
-        <v>0</v>
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF49" s="3">
         <v>0</v>
@@ -4977,8 +5087,11 @@
       <c r="AM49" s="3">
         <v>0</v>
       </c>
+      <c r="AN49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5090,8 +5203,11 @@
       <c r="AM50" s="3">
         <v>0</v>
       </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5203,121 +5319,127 @@
       <c r="AM51" s="3">
         <v>0</v>
       </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E52" s="3">
         <v>11200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8300</v>
-      </c>
-      <c r="G52" s="3">
-        <v>8200</v>
       </c>
       <c r="H52" s="3">
         <v>8200</v>
       </c>
       <c r="I52" s="3">
+        <v>8200</v>
+      </c>
+      <c r="J52" s="3">
         <v>10300</v>
-      </c>
-      <c r="J52" s="3">
-        <v>7900</v>
       </c>
       <c r="K52" s="3">
         <v>7900</v>
       </c>
       <c r="L52" s="3">
+        <v>7900</v>
+      </c>
+      <c r="M52" s="3">
         <v>4100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>191300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>191500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6600</v>
-      </c>
-      <c r="W52" s="3">
-        <v>5800</v>
       </c>
       <c r="X52" s="3">
         <v>5800</v>
       </c>
       <c r="Y52" s="3">
+        <v>5800</v>
+      </c>
+      <c r="Z52" s="3">
         <v>5600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2200</v>
       </c>
-      <c r="AK52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL52" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM52" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN52" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5429,121 +5551,127 @@
       <c r="AM53" s="3">
         <v>0</v>
       </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>896100</v>
+      </c>
+      <c r="E54" s="3">
         <v>825300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>763600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>712300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>661200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>599300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>580600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>555300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>542400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>519700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>526300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>483100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>484300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>442900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>459700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>460000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>210600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>231000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>232800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>252900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>279200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>311200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>349500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>384400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>271400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>226100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>254500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>281800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>308100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>346200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>322000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>347100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>365100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>224800</v>
       </c>
-      <c r="AK54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL54" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM54" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN54" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5583,8 +5711,9 @@
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
     </row>
-    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5624,150 +5753,154 @@
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
     </row>
-    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E57" s="3">
         <v>24400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>6200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>2000</v>
       </c>
       <c r="I57" s="3">
         <v>2000</v>
       </c>
       <c r="J57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K57" s="3">
         <v>8300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>4200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>3900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>4300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>5700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>9300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>10900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>4700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2800</v>
       </c>
-      <c r="AK57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM57" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN57" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2300</v>
-      </c>
-      <c r="I58" s="3">
-        <v>2000</v>
       </c>
       <c r="J58" s="3">
         <v>2000</v>
       </c>
       <c r="K58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L58" s="3">
         <v>2100</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2300</v>
       </c>
       <c r="M58" s="3">
         <v>2300</v>
@@ -5776,14 +5909,14 @@
         <v>2300</v>
       </c>
       <c r="O58" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P58" s="3">
         <v>2200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3500</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -5850,279 +5983,288 @@
       <c r="AM58" s="3">
         <v>0</v>
       </c>
+      <c r="AN58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E59" s="3">
         <v>20700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17100</v>
-      </c>
-      <c r="I59" s="3">
-        <v>16100</v>
       </c>
       <c r="J59" s="3">
         <v>16100</v>
       </c>
       <c r="K59" s="3">
+        <v>16100</v>
+      </c>
+      <c r="L59" s="3">
         <v>11500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>11600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>10800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>39200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>55000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>41000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>47000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>43000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>32800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>34600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>32700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>31300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>21000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>18200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>15100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>22100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>21100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>20800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>30000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>31600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>23400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>22600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>16500</v>
       </c>
-      <c r="AK59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL59" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM59" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN59" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>171200</v>
+      </c>
+      <c r="E60" s="3">
         <v>156600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>139200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>123600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>117800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>97300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>100600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>96000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>84300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>64200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>63700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>53500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>47500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>36600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>47100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>56500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>43500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>50400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>44800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>34400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>38800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>35500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>31800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>24900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>20600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>19300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>27800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>27600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>30200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>36900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>42600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>28000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>19300</v>
       </c>
-      <c r="AK60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL60" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM60" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN60" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E61" s="3">
         <v>5900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>7900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2100</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -6189,34 +6331,37 @@
       <c r="AM61" s="3">
         <v>0</v>
       </c>
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E62" s="3">
         <v>25300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>18500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>14500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>1900</v>
       </c>
       <c r="L62" s="3">
         <v>1900</v>
@@ -6234,67 +6379,67 @@
         <v>1900</v>
       </c>
       <c r="Q62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R62" s="3">
         <v>16500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>19500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>13500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>14400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>4400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>4600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>5000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>5700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>2300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>2800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>2700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>100</v>
-      </c>
-      <c r="AH62" s="3">
-        <v>200</v>
       </c>
       <c r="AI62" s="3">
         <v>200</v>
       </c>
       <c r="AJ62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK62" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="AK62" s="3">
+        <v>0</v>
       </c>
       <c r="AL62" s="3" t="s">
         <v>3</v>
@@ -6302,8 +6447,11 @@
       <c r="AM62" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN62" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6415,8 +6563,11 @@
       <c r="AM63" s="3">
         <v>0</v>
       </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6528,8 +6679,11 @@
       <c r="AM64" s="3">
         <v>0</v>
       </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6641,121 +6795,127 @@
       <c r="AM65" s="3">
         <v>0</v>
       </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>242000</v>
+      </c>
+      <c r="E66" s="3">
         <v>219600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>196000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>177000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>166100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>141800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>142100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>118300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>107300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>87800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>87500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>77900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>72700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>52800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>63500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>75900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>57100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>64700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>47800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>38800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>43400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>40500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>37500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>25900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>21000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>20300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>29100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>29900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>32900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>39600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>42700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>28200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>23300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>19300</v>
       </c>
-      <c r="AK66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL66" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM66" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN66" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6795,8 +6955,9 @@
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
     </row>
-    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6908,8 +7069,11 @@
       <c r="AM68" s="3">
         <v>0</v>
       </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7021,8 +7185,11 @@
       <c r="AM69" s="3">
         <v>0</v>
       </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7123,19 +7290,22 @@
         <v>0</v>
       </c>
       <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
         <v>310600</v>
       </c>
-      <c r="AK70" s="3">
-        <v>0</v>
-      </c>
       <c r="AL70" s="3">
         <v>0</v>
       </c>
       <c r="AM70" s="3">
         <v>0</v>
       </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7247,121 +7417,127 @@
       <c r="AM71" s="3">
         <v>0</v>
       </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-414100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-439500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-462100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-476300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-494800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-512600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-521100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-512300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-499600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-495700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-478000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-503200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-489300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-504300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-492000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-496500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-720600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-700600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-675400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-639100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-608500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-567000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-517500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-463800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-420000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-382500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-356100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-324300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-297200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-260000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-194200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-151600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-127200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-107000</v>
       </c>
-      <c r="AK72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM72" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN72" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7473,8 +7649,11 @@
       <c r="AM73" s="3">
         <v>0</v>
       </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7586,8 +7765,11 @@
       <c r="AM74" s="3">
         <v>0</v>
       </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7699,121 +7881,127 @@
       <c r="AM75" s="3">
         <v>0</v>
       </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>654100</v>
+      </c>
+      <c r="E76" s="3">
         <v>605700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>567600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>535400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>495000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>457500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>438400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>437000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>435100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>431900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>438800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>405100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>411700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>390100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>396100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>384000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>153500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>166200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>185000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>214000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>235800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>270700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>311900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>358500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>250400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>205800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>225400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>251900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>275200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>306500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>279300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>318900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>341800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>-105100</v>
       </c>
-      <c r="AK76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AL76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AM76" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="AN76" s="3" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7925,239 +8113,248 @@
       <c r="AM77" s="3">
         <v>0</v>
       </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
     </row>
-    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E81" s="3">
         <v>22600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>14200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>18400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>8500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-8900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-12700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-17700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>25200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>15000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>224100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-20000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-25200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-36300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-30500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-41600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-49500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-53700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-43800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-37500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-26400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-31800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-27100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-37200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-65800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-42600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-24400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-20300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-64900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-16000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>-11200</v>
       </c>
     </row>
-    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8197,16 +8394,17 @@
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
     </row>
-    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>400</v>
+      </c>
+      <c r="E83" s="3">
         <v>300</v>
-      </c>
-      <c r="E83" s="3">
-        <v>400</v>
       </c>
       <c r="F83" s="3">
         <v>400</v>
@@ -8215,13 +8413,13 @@
         <v>400</v>
       </c>
       <c r="H83" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I83" s="3">
         <v>500</v>
       </c>
       <c r="J83" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="K83" s="3">
         <v>600</v>
@@ -8233,22 +8431,22 @@
         <v>600</v>
       </c>
       <c r="N83" s="3">
+        <v>600</v>
+      </c>
+      <c r="O83" s="3">
         <v>500</v>
-      </c>
-      <c r="O83" s="3">
-        <v>700</v>
       </c>
       <c r="P83" s="3">
         <v>700</v>
       </c>
       <c r="Q83" s="3">
+        <v>700</v>
+      </c>
+      <c r="R83" s="3">
         <v>600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>500</v>
-      </c>
-      <c r="S83" s="3">
-        <v>700</v>
       </c>
       <c r="T83" s="3">
         <v>700</v>
@@ -8263,10 +8461,10 @@
         <v>700</v>
       </c>
       <c r="X83" s="3">
+        <v>700</v>
+      </c>
+      <c r="Y83" s="3">
         <v>300</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>600</v>
       </c>
       <c r="Z83" s="3">
         <v>600</v>
@@ -8281,7 +8479,7 @@
         <v>600</v>
       </c>
       <c r="AD83" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AE83" s="3">
         <v>500</v>
@@ -8290,11 +8488,11 @@
         <v>500</v>
       </c>
       <c r="AG83" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH83" s="3">
         <v>300</v>
       </c>
-      <c r="AH83" s="3">
-        <v>0</v>
-      </c>
       <c r="AI83" s="3">
         <v>0</v>
       </c>
@@ -8310,8 +8508,11 @@
       <c r="AM83" s="3">
         <v>0</v>
       </c>
+      <c r="AN83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8423,8 +8624,11 @@
       <c r="AM84" s="3">
         <v>0</v>
       </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8536,8 +8740,11 @@
       <c r="AM85" s="3">
         <v>0</v>
       </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8649,8 +8856,11 @@
       <c r="AM86" s="3">
         <v>0</v>
       </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8762,8 +8972,11 @@
       <c r="AM87" s="3">
         <v>0</v>
       </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8875,121 +9088,127 @@
       <c r="AM88" s="3">
         <v>0</v>
       </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E89" s="3">
         <v>50200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>53900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>33700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>28100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>22300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>18800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>17000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-3700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-11600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>62100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-7800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-36800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-18900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-28500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-38800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-40100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-41200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-34300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-29200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-31800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-24200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-29300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-41700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-63300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-27600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-20500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-15000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-50200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-10900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-10200</v>
       </c>
     </row>
-    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9029,43 +9248,44 @@
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
     </row>
-    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
       <c r="L91" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>-100</v>
       </c>
       <c r="N91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
@@ -9080,16 +9300,16 @@
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-300</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-100</v>
       </c>
       <c r="W91" s="3">
         <v>-100</v>
@@ -9101,49 +9321,52 @@
         <v>-100</v>
       </c>
       <c r="Z91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
       </c>
       <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-200</v>
-      </c>
-      <c r="AJ91" s="3">
-        <v>-100</v>
       </c>
       <c r="AK91" s="3">
         <v>-100</v>
       </c>
       <c r="AL91" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AM91" s="3">
         <v>0</v>
       </c>
+      <c r="AN91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9255,8 +9478,11 @@
       <c r="AM92" s="3">
         <v>0</v>
       </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9368,121 +9594,127 @@
       <c r="AM93" s="3">
         <v>0</v>
       </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-73600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-31900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-70800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-62800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-51500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>65300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-46800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>25500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-14900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-12300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>35500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-37900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-42700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>19000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>38300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-22700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-50000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>47800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>86000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>44800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>68600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-149700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-31200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>88800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>1900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>15200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>41400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>29700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-194900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-73900</v>
-      </c>
-      <c r="AJ94" s="3">
-        <v>-100</v>
       </c>
       <c r="AK94" s="3">
         <v>-100</v>
       </c>
       <c r="AL94" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AM94" s="3">
         <v>0</v>
       </c>
+      <c r="AN94" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9522,8 +9754,9 @@
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
     </row>
-    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9566,8 +9799,8 @@
       <c r="P96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -9635,8 +9868,11 @@
       <c r="AM96" s="3">
         <v>0</v>
       </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9748,8 +9984,11 @@
       <c r="AM97" s="3">
         <v>0</v>
       </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9861,8 +10100,11 @@
       <c r="AM98" s="3">
         <v>0</v>
       </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9974,121 +10216,127 @@
       <c r="AM99" s="3">
         <v>0</v>
       </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12100</v>
+      </c>
+      <c r="E100" s="3">
         <v>6100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>7700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>11900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>10700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>3600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>146400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>77600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>83200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>156400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>190800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>39900</v>
       </c>
-      <c r="AL100" s="3">
-        <v>0</v>
-      </c>
       <c r="AM100" s="3">
         <v>0</v>
       </c>
+      <c r="AN100" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10131,8 +10379,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10200,117 +10448,123 @@
       <c r="AM101" s="3">
         <v>0</v>
       </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E102" s="3">
         <v>24400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>34900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-26400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>86200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-41800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>33100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>5300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>31900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-42100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-53000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>81500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>31000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-59100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-67700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>22000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>48100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>28200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-37600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>17100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>59400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-21900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-14000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>10700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>2300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-216100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>64600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>175800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-10400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-11000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-10200</v>
       </c>
     </row>
